--- a/informed_consent_forms/049_telehealth_patient_consent_form--informed_consent_forms.xlsx
+++ b/informed_consent_forms/049_telehealth_patient_consent_form--informed_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date (2)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time (2)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date of Signature</t>
+          <t>Provider Signature Date</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Time of Signature</t>
+          <t>Provider Signature Time</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>I Have Agreed to the Terms and Conditions</t>
+          <t>Provider Agreed</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Provider Agreed Note</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'patient_signature_1',_'value':_'patient_signature_1'}</t>
+          <t>patient_signature_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Patient Signature 1', 'value': 'patient_signature_1'}</t>
+          <t>Patient Signature 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'patient_signature_2',_'value':_'patient_signature_2'}</t>
+          <t>patient_signature_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Patient Signature 2', 'value': 'patient_signature_2'}</t>
+          <t>Patient Signature 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'provider_1',_'value':_'provider_1'}</t>
+          <t>provider_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Provider 1', 'value': 'provider_1'}</t>
+          <t>Provider 1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree_to_the_terms_and_conditions',_'value':_true}</t>
+          <t>i_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I agree to the Terms and Conditions', 'value': True}</t>
+          <t>I agree to the Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_agree',_'value':_false}</t>
+          <t>not_agree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not Agree', 'value': False}</t>
+          <t>Not Agree</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree_to_the_terms_and_conditions',_'value':_true}</t>
+          <t>i_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'I agree to the Terms and Conditions', 'value': True}</t>
+          <t>I agree to the Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'not_agree',_'value':_false}</t>
+          <t>not_agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Not Agree', 'value': False}</t>
+          <t>Not Agree</t>
         </is>
       </c>
     </row>
